--- a/Plotting/Results_excels/production_shares_olefins_Scope1-2_FPO.xlsx
+++ b/Plotting/Results_excels/production_shares_olefins_Scope1-2_FPO.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,13 +483,6 @@
       </c>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Iteration_3</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -542,26 +535,11 @@
           <t>2050</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Conventional</t>
+          <t>Conventional (fossil)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -591,20 +569,11 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Carbon Capture</t>
+          <t>Conventional (fossil) with CC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -632,15 +601,6 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -660,31 +620,22 @@
         <v>1052661.907550473</v>
       </c>
       <c r="E6" t="n">
-        <v>1717666.256705007</v>
+        <v>1717666.256705052</v>
       </c>
       <c r="F6" t="n">
-        <v>1291082.684622778</v>
+        <v>1290306.091312084</v>
       </c>
       <c r="G6" t="n">
-        <v>1421518.068604012</v>
+        <v>1692208.535193708</v>
       </c>
       <c r="H6" t="n">
-        <v>1717666.256705079</v>
+        <v>1717666.256705083</v>
       </c>
       <c r="I6" t="n">
-        <v>1291551.640803284</v>
+        <v>1291310.275516131</v>
       </c>
       <c r="J6" t="n">
-        <v>1394401.740586543</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1717666.256704633</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1291333.422612885</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1416048.659306949</v>
+        <v>1693910.224569886</v>
       </c>
     </row>
     <row r="7">
@@ -720,15 +671,6 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -746,31 +688,22 @@
         <v>664866.4223266498</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.00498988138784e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>426495.0954895906</v>
+        <v>427271.5277290774</v>
       </c>
       <c r="G8" t="n">
-        <v>296086.7647731616</v>
+        <v>25452.44139135936</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>426026.2365740693</v>
+        <v>426267.5518002738</v>
       </c>
       <c r="J8" t="n">
-        <v>323197.4686633368</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.331641708114567e-07</v>
-      </c>
-      <c r="L8" t="n">
-        <v>426244.409504575</v>
-      </c>
-      <c r="M8" t="n">
-        <v>301555.0396739647</v>
+        <v>23751.10495817134</v>
       </c>
     </row>
     <row r="9">
@@ -806,15 +739,6 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -849,15 +773,6 @@
       <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -892,15 +807,6 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -935,15 +841,6 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -978,15 +875,6 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1021,15 +909,6 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1064,15 +943,6 @@
       <c r="J15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1107,22 +977,12 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
-    <mergeCell ref="K1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
